--- a/patient_registration_form_templates/029_palliative_care_discharge_form--patient_registration_form_templates.xlsx
+++ b/patient_registration_form_templates/029_palliative_care_discharge_form--patient_registration_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1160,34 +1160,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patient_status_choices</t>
+          <t>medications_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>acetaminophen</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>acetaminophen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>patient_status_choices</t>
+          <t>medications_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>aspirin</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>aspirin</t>
         </is>
       </c>
     </row>
@@ -1199,36 +1199,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>acetaminophen</t>
+          <t>ibuprofen</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>acetaminophen</t>
+          <t>ibuprofen</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medications_choices</t>
+          <t>allergies_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>aspirin</t>
+          <t>penicillin</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>aspirin</t>
+          <t>penicillin</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>medications_choices</t>
+          <t>allergies_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1250,46 +1250,46 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>penicillin</t>
+          <t>acetaminophen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>penicillin</t>
+          <t>acetaminophen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>medical_history_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ibuprofen</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ibuprofen</t>
+          <t>heart</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>allergies_choices</t>
+          <t>medical_history_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>acetaminophen</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>acetaminophen</t>
+          <t>diabetes</t>
         </is>
       </c>
     </row>
@@ -1301,36 +1301,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>kidney</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>medical_history_2_choices</t>
+          <t>medical_history_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>diabetes</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>diabetes</t>
+          <t>heart</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>medical_history_2_choices</t>
+          <t>medical_history_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1352,46 +1352,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>liver</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medical_history_3_choices</t>
+          <t>medical_history_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>liver</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>medical_history_3_choices</t>
+          <t>medical_history_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>brain</t>
         </is>
       </c>
     </row>
@@ -1403,19 +1403,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>lung</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>lung</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>medical_history_4_choices</t>
+          <t>medical_history_5_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>medical_history_4_choices</t>
+          <t>medical_history_5_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1454,46 +1454,46 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>heart</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>medical_history_5_choices</t>
+          <t>medical_history_6_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lung</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lung</t>
+          <t>kidney</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>medical_history_5_choices</t>
+          <t>medical_history_6_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>lung</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>lung</t>
         </is>
       </c>
     </row>
@@ -1505,19 +1505,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>heart</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>heart</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>medical_history_6_choices</t>
+          <t>medical_history_7_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,17 +1534,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>medical_history_6_choices</t>
+          <t>medical_history_7_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>heart</t>
+          <t>liver</t>
         </is>
       </c>
     </row>
@@ -1556,19 +1556,19 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>lung</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>lung</t>
+          <t>brain</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>medical_history_7_choices</t>
+          <t>medical_history_8_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>medical_history_7_choices</t>
+          <t>medical_history_8_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1607,19 +1607,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>kidney</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>medical_history_8_choices</t>
+          <t>medical_history_9_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>medical_history_8_choices</t>
+          <t>medical_history_9_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1658,19 +1658,19 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>liver</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>medical_history_9_choices</t>
+          <t>medical_history_10_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>medical_history_9_choices</t>
+          <t>medical_history_10_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1709,19 +1709,19 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>brain</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>kidney</t>
+          <t>brain</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>medical_history_10_choices</t>
+          <t>medical_history_11_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>medical_history_10_choices</t>
+          <t>medical_history_11_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1760,19 +1760,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>kidney</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>liver</t>
+          <t>kidney</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>medical_history_11_choices</t>
+          <t>medical_history_12_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>medical_history_11_choices</t>
+          <t>medical_history_12_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1811,44 +1811,10 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>brain</t>
+          <t>liver</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
-        <is>
-          <t>brain</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>medical_history_12_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>kidney</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>kidney</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>medical_history_12_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>liver</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
         <is>
           <t>liver</t>
         </is>
